--- a/output/Data and Chart Outputs/mexico_gas.xlsx
+++ b/output/Data and Chart Outputs/mexico_gas.xlsx
@@ -152,7 +152,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Mexico gas imports from the US (EIA, US export data) (to Jul/26)</a:t>
+              <a:t>Mexico pipeline gas imports from the US (EIA, US export data) (to Jul/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -188,34 +188,6 @@
           <val>
             <numRef>
               <f>'Chart'!$B$2:$B$68</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Chart'!C1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="EB6834"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Chart'!$A$2:$A$68</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Chart'!$C$2:$C$68</f>
             </numRef>
           </val>
         </ser>
@@ -287,10 +259,6 @@
         </a:ln>
       </spPr>
     </plotArea>
-    <legend>
-      <legendPos val="b"/>
-      <overlay val="0"/>
-    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -307,7 +275,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>3</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -619,7 +587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -646,38 +614,45 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>LNG_imports_from_US is EIA's series as published, but it has months of 2-3.5 Bcf/d (20-25% of all US LNG exports) among months of ~0.1 Bcf/d, which is not credible; it is kept here but not charted. Pipeline imports are the meaningful series (they match EIA's US pipeline exports to Mexico).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>COVERAGE</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Jan 2015 to Jul 2026. Mexico's own demand-by-sector statistics (SENER SIE) are not pulled yet.</t>
         </is>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>SOURCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>EIA API v2: N9132MX2 (US natural gas pipeline exports to Mexico), N9133MX2 (US LNG exports to Mexico).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
+        <is>
+          <t>EIA API v2: N9132MX2 (US natural gas pipeline exports to Mexico), N9133MX2 (US LNG exports to Mexico).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>https://www.eia.gov/dnav/ng/ng_move_expc_s1_m.htm</t>
         </is>
@@ -694,7 +669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:B68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -711,11 +686,6 @@
           <t>Pipeline from the US</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>LNG from the US</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -724,9 +694,6 @@
       <c r="B2" t="n">
         <v>5.592</v>
       </c>
-      <c r="C2" t="n">
-        <v>0.003</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -735,9 +702,6 @@
       <c r="B3" t="n">
         <v>4.906</v>
       </c>
-      <c r="C3" t="n">
-        <v>0.479</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -746,9 +710,6 @@
       <c r="B4" t="n">
         <v>5.905</v>
       </c>
-      <c r="C4" t="n">
-        <v>0.001</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -757,9 +718,6 @@
       <c r="B5" t="n">
         <v>6.097</v>
       </c>
-      <c r="C5" t="n">
-        <v>0.002</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -768,9 +726,6 @@
       <c r="B6" t="n">
         <v>6.211</v>
       </c>
-      <c r="C6" t="n">
-        <v>0.002</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -779,9 +734,6 @@
       <c r="B7" t="n">
         <v>6.608</v>
       </c>
-      <c r="C7" t="n">
-        <v>0.004</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -790,9 +742,6 @@
       <c r="B8" t="n">
         <v>6.375</v>
       </c>
-      <c r="C8" t="n">
-        <v>0.028</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -801,9 +750,6 @@
       <c r="B9" t="n">
         <v>6.249</v>
       </c>
-      <c r="C9" t="n">
-        <v>0.005</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -812,9 +758,6 @@
       <c r="B10" t="n">
         <v>5.958</v>
       </c>
-      <c r="C10" t="n">
-        <v>0.005</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -823,9 +766,6 @@
       <c r="B11" t="n">
         <v>5.951</v>
       </c>
-      <c r="C11" t="n">
-        <v>0.041</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -834,9 +774,6 @@
       <c r="B12" t="n">
         <v>5.515</v>
       </c>
-      <c r="C12" t="n">
-        <v>0.005</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -845,9 +782,6 @@
       <c r="B13" t="n">
         <v>5.386</v>
       </c>
-      <c r="C13" t="n">
-        <v>0.005</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -856,9 +790,6 @@
       <c r="B14" t="n">
         <v>5.66</v>
       </c>
-      <c r="C14" t="n">
-        <v>0.005</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -867,9 +798,6 @@
       <c r="B15" t="n">
         <v>5.537</v>
       </c>
-      <c r="C15" t="n">
-        <v>0.006</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -878,9 +806,6 @@
       <c r="B16" t="n">
         <v>5.48</v>
       </c>
-      <c r="C16" t="n">
-        <v>0.005</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -889,9 +814,6 @@
       <c r="B17" t="n">
         <v>5.882</v>
       </c>
-      <c r="C17" t="n">
-        <v>0.004</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -900,9 +822,6 @@
       <c r="B18" t="n">
         <v>6</v>
       </c>
-      <c r="C18" t="n">
-        <v>0.004</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -911,9 +830,6 @@
       <c r="B19" t="n">
         <v>6.1</v>
       </c>
-      <c r="C19" t="n">
-        <v>0.113</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -922,9 +838,6 @@
       <c r="B20" t="n">
         <v>6.118</v>
       </c>
-      <c r="C20" t="n">
-        <v>0.002</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -933,9 +846,6 @@
       <c r="B21" t="n">
         <v>5.89</v>
       </c>
-      <c r="C21" t="n">
-        <v>0.003</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -944,9 +854,6 @@
       <c r="B22" t="n">
         <v>5.639</v>
       </c>
-      <c r="C22" t="n">
-        <v>0.003</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -955,9 +862,6 @@
       <c r="B23" t="n">
         <v>5.541</v>
       </c>
-      <c r="C23" t="n">
-        <v>0.006</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -966,9 +870,6 @@
       <c r="B24" t="n">
         <v>5.366</v>
       </c>
-      <c r="C24" t="n">
-        <v>0.005</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -977,9 +878,6 @@
       <c r="B25" t="n">
         <v>5.117</v>
       </c>
-      <c r="C25" t="n">
-        <v>0.023</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -988,9 +886,6 @@
       <c r="B26" t="n">
         <v>5.356</v>
       </c>
-      <c r="C26" t="n">
-        <v>0.108</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -999,9 +894,6 @@
       <c r="B27" t="n">
         <v>5.457</v>
       </c>
-      <c r="C27" t="n">
-        <v>0.004</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -1010,9 +902,6 @@
       <c r="B28" t="n">
         <v>5.731</v>
       </c>
-      <c r="C28" t="n">
-        <v>0.101</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -1021,9 +910,6 @@
       <c r="B29" t="n">
         <v>5.639</v>
       </c>
-      <c r="C29" t="n">
-        <v>0.002</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -1032,9 +918,6 @@
       <c r="B30" t="n">
         <v>6.246</v>
       </c>
-      <c r="C30" t="n">
-        <v>0.001</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -1043,9 +926,6 @@
       <c r="B31" t="n">
         <v>6.804</v>
       </c>
-      <c r="C31" t="n">
-        <v>0.001</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -1054,9 +934,6 @@
       <c r="B32" t="n">
         <v>6.73</v>
       </c>
-      <c r="C32" t="n">
-        <v>0.064</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -1065,9 +942,6 @@
       <c r="B33" t="n">
         <v>6.873</v>
       </c>
-      <c r="C33" t="n">
-        <v>0.001</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -1076,9 +950,6 @@
       <c r="B34" t="n">
         <v>6.747</v>
       </c>
-      <c r="C34" t="n">
-        <v>0.001</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -1087,9 +958,6 @@
       <c r="B35" t="n">
         <v>6.467</v>
       </c>
-      <c r="C35" t="n">
-        <v>0.058</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -1098,9 +966,6 @@
       <c r="B36" t="n">
         <v>5.967</v>
       </c>
-      <c r="C36" t="n">
-        <v>0.001</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -1109,9 +974,6 @@
       <c r="B37" t="n">
         <v>5.632</v>
       </c>
-      <c r="C37" t="n">
-        <v>0.119</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -1120,9 +982,6 @@
       <c r="B38" t="n">
         <v>5.986</v>
       </c>
-      <c r="C38" t="n">
-        <v>2.622</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -1131,9 +990,6 @@
       <c r="B39" t="n">
         <v>5.86</v>
       </c>
-      <c r="C39" t="n">
-        <v>0.108</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -1142,9 +998,6 @@
       <c r="B40" t="n">
         <v>5.885</v>
       </c>
-      <c r="C40" t="n">
-        <v>0.012</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -1153,9 +1006,6 @@
       <c r="B41" t="n">
         <v>6.362</v>
       </c>
-      <c r="C41" t="n">
-        <v>0.014</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -1164,9 +1014,6 @@
       <c r="B42" t="n">
         <v>6.842</v>
       </c>
-      <c r="C42" t="n">
-        <v>3.204</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -1175,9 +1022,6 @@
       <c r="B43" t="n">
         <v>6.791</v>
       </c>
-      <c r="C43" t="n">
-        <v>0.048</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -1186,9 +1030,6 @@
       <c r="B44" t="n">
         <v>7.028</v>
       </c>
-      <c r="C44" t="n">
-        <v>0.012</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -1197,9 +1038,6 @@
       <c r="B45" t="n">
         <v>7.119</v>
       </c>
-      <c r="C45" t="n">
-        <v>0.759</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -1208,9 +1046,6 @@
       <c r="B46" t="n">
         <v>6.851</v>
       </c>
-      <c r="C46" t="n">
-        <v>0.004</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -1219,9 +1054,6 @@
       <c r="B47" t="n">
         <v>6.492</v>
       </c>
-      <c r="C47" t="n">
-        <v>2.55</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -1230,9 +1062,6 @@
       <c r="B48" t="n">
         <v>5.93</v>
       </c>
-      <c r="C48" t="n">
-        <v>0.001</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -1241,9 +1070,6 @@
       <c r="B49" t="n">
         <v>5.636</v>
       </c>
-      <c r="C49" t="n">
-        <v>1.986</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -1276,9 +1102,6 @@
       <c r="B53" t="n">
         <v>6.678</v>
       </c>
-      <c r="C53" t="n">
-        <v>3.498</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -1303,9 +1126,6 @@
       <c r="B56" t="n">
         <v>6.882</v>
       </c>
-      <c r="C56" t="n">
-        <v>1.501</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -1314,9 +1134,6 @@
       <c r="B57" t="n">
         <v>7.39</v>
       </c>
-      <c r="C57" t="n">
-        <v>3.231</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -1341,9 +1158,6 @@
       <c r="B60" t="n">
         <v>6.241</v>
       </c>
-      <c r="C60" t="n">
-        <v>2.824</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -1376,9 +1190,6 @@
       <c r="B64" t="n">
         <v>6.351</v>
       </c>
-      <c r="C64" t="n">
-        <v>0.098</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -1402,9 +1213,6 @@
       </c>
       <c r="B67" t="n">
         <v>7.54</v>
-      </c>
-      <c r="C67" t="n">
-        <v>0.096</v>
       </c>
     </row>
     <row r="68">

--- a/output/Data and Chart Outputs/mexico_gas.xlsx
+++ b/output/Data and Chart Outputs/mexico_gas.xlsx
@@ -152,6 +152,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Mexico pipeline gas imports from the US (EIA, US export data) (to Jul/26)</a:t>
             </a:r>
           </a:p>
